--- a/data/ams_weekly_data/Tonor/business_report_week26.xlsx
+++ b/data/ams_weekly_data/Tonor/business_report_week26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,11 @@
           <t>B01ISNU3X4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
@@ -643,7 +647,11 @@
           <t>B078WNW4YW</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
@@ -720,7 +728,11 @@
           <t>B07GVGMW59</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
@@ -874,7 +886,11 @@
           <t>B07WLWN2ZT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TC-777</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
@@ -951,7 +967,11 @@
           <t>B082W4B7SX</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -1087,25 +1107,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA77111</t>
+          <t>FBA77104</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TC30</t>
+          <t>TC20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B089SJGQBH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>B089SJGQBH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TC20</t>
+        </is>
+      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -1137,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1149,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>13044.92</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1164,25 +1188,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA77110</t>
+          <t>FBA77111</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TM20</t>
+          <t>TC30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>B08CVP2HXP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TC30</t>
+        </is>
+      </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
@@ -1226,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>17790.69</v>
+        <v>13044.92</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1241,25 +1269,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA77115</t>
+          <t>FBA77110</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TC40</t>
+          <t>TM20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>B08NDB5NWP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TM20</t>
+        </is>
+      </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
@@ -1291,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1303,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>17790.69</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1318,25 +1350,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79576</t>
+          <t>FBA77115</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TC30S+</t>
+          <t>TC40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>B08V1JS3NY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TC40</t>
+        </is>
+      </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
@@ -1368,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1380,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2372.03</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1395,25 +1431,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79113</t>
+          <t>FBA77103</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TC310</t>
+          <t>ORCA001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>B09Z5Q194D</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ORCA001</t>
+        </is>
+      </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
@@ -1445,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1457,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2117.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1472,25 +1512,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA79574</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TC-777 PRO</t>
+          <t>TC30S</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>B0B4WTHLX5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TC30S</t>
+        </is>
+      </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
@@ -1522,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1534,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>18634.73</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1549,25 +1593,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79114</t>
+          <t>FBA77116</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TC310+</t>
+          <t>TC40S</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>B0BBL47VR5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TC40S</t>
+        </is>
+      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -1599,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1611,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>12283.9</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1626,25 +1674,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA79576</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>TC30S+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>B0BRCR2QQ7</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TC30S+</t>
+        </is>
+      </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
@@ -1676,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1688,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2372.03</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1703,25 +1755,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79696</t>
+          <t>FBA79111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TD310+</t>
+          <t>TD510</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>B0BRKFP94K</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TD510</t>
+        </is>
+      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
@@ -1753,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1765,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>9317.799999999999</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1780,25 +1836,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79697</t>
+          <t>FBA79113</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TD310</t>
+          <t>TC310</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>B0BTCXQQ6M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TC310</t>
+        </is>
+      </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
@@ -1830,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1842,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>20328.79</v>
+        <v>2117.8</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1857,77 +1917,648 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>FBK77102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0BVHZ5MKZ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B0BVHZ5MKZ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FBA79116</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TC-777 PRO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0BYHHSLPC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B0BYHHSLPC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TC-777 PRO</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18634.73</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FBA79114</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TC310+</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0CCV74CL7</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B0CCV74CL7</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TC310+</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>12283.9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FBA79585</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>T20LP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>T20LP</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FBA79586</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TRL-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0CH9JR3HL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B0CH9JR3HL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TRL-20</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FBA79696</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TD310+</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0CQX3VB1R</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B0CQX3VB1R</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TD310+</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>9317.799999999999</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FBA79697</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TD310</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0CQX4K9P5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B0CQX4K9P5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TD310</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>20328.79</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>FBA79577</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>TM310</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>B0CSCT63BL</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>B0CSCT63BL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TM310</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/ams_weekly_data/Tonor/business_report_week26.xlsx
+++ b/data/ams_weekly_data/Tonor/business_report_week26.xlsx
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20585.56</v>
+        <v>27447.42</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4150.84</v>
+        <v>8301.690000000001</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2117.8</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>18634.73</v>
+        <v>22056.76</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>12283.9</v>
+        <v>19654.24</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>8894.07</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2117.8</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2550,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2033.05</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
